--- a/new-model/matlab/result3.xlsx
+++ b/new-model/matlab/result3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="126" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="20">
   <si>
     <t>无人机编号</t>
   </si>
@@ -122,16 +122,16 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="true"/>
-    <col min="2" max="2" width="11.5546875" customWidth="true"/>
-    <col min="3" max="3" width="11.5546875" customWidth="true"/>
+    <col min="2" max="2" width="6.77734375" customWidth="true"/>
+    <col min="3" max="3" width="9.21875" customWidth="true"/>
     <col min="4" max="4" width="11" customWidth="true"/>
     <col min="5" max="5" width="11.5546875" customWidth="true"/>
     <col min="6" max="6" width="12.21875" customWidth="true"/>
     <col min="7" max="7" width="7.77734375" customWidth="true"/>
     <col min="8" max="8" width="11.5546875" customWidth="true"/>
     <col min="9" max="9" width="12.21875" customWidth="true"/>
-    <col min="10" max="10" width="8.5546875" customWidth="true"/>
-    <col min="11" max="11" width="13.5546875" customWidth="true"/>
+    <col min="10" max="10" width="10.5546875" customWidth="true"/>
+    <col min="11" max="11" width="13" customWidth="true"/>
     <col min="12" max="12" width="13" customWidth="true"/>
   </cols>
   <sheetData>
@@ -178,10 +178,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C2" s="0">
-        <v>100.5</v>
+        <v>107</v>
       </c>
       <c r="D2" s="0">
         <v>1</v>
@@ -196,16 +196,16 @@
         <v>1800</v>
       </c>
       <c r="H2" s="0">
-        <v>17498.913195271496</v>
+        <v>17479.195544526869</v>
       </c>
       <c r="I2" s="0">
-        <v>15.779290807247557</v>
+        <v>11.202738441502866</v>
       </c>
       <c r="J2" s="0">
         <v>1755.9000000000001</v>
       </c>
       <c r="K2" s="0">
-        <v>3.2778991699218754</v>
+        <v>4.4749694824218746</v>
       </c>
       <c r="L2" s="0" t="s">
         <v>17</v>
@@ -216,28 +216,28 @@
         <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C3" s="0">
-        <v>100.5</v>
+        <v>107</v>
       </c>
       <c r="D3" s="0">
         <v>2</v>
       </c>
       <c r="E3" s="0">
-        <v>17699.637731757164</v>
+        <v>17693.065181508955</v>
       </c>
       <c r="F3" s="0">
-        <v>5.2597636024158527</v>
+        <v>3.7342461471676223</v>
       </c>
       <c r="G3" s="0">
         <v>1800</v>
       </c>
       <c r="H3" s="0">
-        <v>17699.637731757164</v>
+        <v>17693.065181508955</v>
       </c>
       <c r="I3" s="0">
-        <v>5.2597636024158527</v>
+        <v>3.7342461471676223</v>
       </c>
       <c r="J3" s="0">
         <v>1800</v>
@@ -254,28 +254,28 @@
         <v>1</v>
       </c>
       <c r="B4" s="0">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C4" s="0">
-        <v>100.5</v>
+        <v>107</v>
       </c>
       <c r="D4" s="0">
         <v>3</v>
       </c>
       <c r="E4" s="0">
-        <v>17599.275463514332</v>
+        <v>17586.130363017914</v>
       </c>
       <c r="F4" s="0">
-        <v>10.519527204831705</v>
+        <v>7.4684922943352445</v>
       </c>
       <c r="G4" s="0">
         <v>1800</v>
       </c>
       <c r="H4" s="0">
-        <v>17599.275463514332</v>
+        <v>17586.130363017914</v>
       </c>
       <c r="I4" s="0">
-        <v>10.519527204831705</v>
+        <v>7.4684922943352445</v>
       </c>
       <c r="J4" s="0">
         <v>1800</v>
@@ -292,34 +292,34 @@
         <v>2</v>
       </c>
       <c r="B5" s="0">
-        <v>225</v>
+        <v>280</v>
       </c>
       <c r="C5" s="0">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D5" s="0">
         <v>1</v>
       </c>
       <c r="E5" s="0">
-        <v>11257.537879754125</v>
+        <v>12126.728440061326</v>
       </c>
       <c r="F5" s="0">
-        <v>657.53787975412513</v>
+        <v>681.28730185169059</v>
       </c>
       <c r="G5" s="0">
         <v>1400</v>
       </c>
       <c r="H5" s="0">
-        <v>10960.553031655776</v>
+        <v>12173.092503498396</v>
       </c>
       <c r="I5" s="0">
-        <v>360.55303165577522</v>
+        <v>418.34363179743099</v>
       </c>
       <c r="J5" s="0">
-        <v>1223.5999999999999</v>
+        <v>1355.9000000000001</v>
       </c>
       <c r="K5" s="0">
-        <v>3.3080261230468793</v>
+        <v>3.8393371582031222</v>
       </c>
       <c r="L5" s="0" t="s">
         <v>18</v>
@@ -330,34 +330,34 @@
         <v>2</v>
       </c>
       <c r="B6" s="0">
-        <v>225</v>
+        <v>280</v>
       </c>
       <c r="C6" s="0">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D6" s="0">
         <v>2</v>
       </c>
       <c r="E6" s="0">
-        <v>11208.040405071066</v>
+        <v>12142.183127873683</v>
       </c>
       <c r="F6" s="0">
-        <v>608.04040507106686</v>
+        <v>593.63941183360407</v>
       </c>
       <c r="G6" s="0">
         <v>1400</v>
       </c>
       <c r="H6" s="0">
-        <v>11133.794193046479</v>
+        <v>12176.956175451485</v>
       </c>
       <c r="I6" s="0">
-        <v>533.79419304647934</v>
+        <v>396.43165929290939</v>
       </c>
       <c r="J6" s="0">
-        <v>1388.9749999999999</v>
+        <v>1375.1937499999999</v>
       </c>
       <c r="K6" s="0">
-        <v>0</v>
+        <v>3.5428833007812557</v>
       </c>
       <c r="L6" s="0" t="s">
         <v>18</v>
@@ -368,28 +368,28 @@
         <v>2</v>
       </c>
       <c r="B7" s="0">
-        <v>225</v>
+        <v>280</v>
       </c>
       <c r="C7" s="0">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D7" s="0">
         <v>3</v>
       </c>
       <c r="E7" s="0">
-        <v>11158.542930388008</v>
+        <v>12157.637815686039</v>
       </c>
       <c r="F7" s="0">
-        <v>558.54293038800847</v>
+        <v>505.99152181551756</v>
       </c>
       <c r="G7" s="0">
         <v>1400</v>
       </c>
       <c r="H7" s="0">
-        <v>11158.542930388008</v>
+        <v>12157.637815686039</v>
       </c>
       <c r="I7" s="0">
-        <v>558.54293038800847</v>
+        <v>505.99152181551756</v>
       </c>
       <c r="J7" s="0">
         <v>1400</v>
@@ -406,34 +406,34 @@
         <v>3</v>
       </c>
       <c r="B8" s="0">
-        <v>71.56781671856767</v>
+        <v>82</v>
       </c>
       <c r="C8" s="0">
-        <v>72.61140725458516</v>
+        <v>117</v>
       </c>
       <c r="D8" s="0">
         <v>1</v>
       </c>
       <c r="E8" s="0">
-        <v>6998.523556227703</v>
+        <v>6384.2847663709326</v>
       </c>
       <c r="F8" s="0">
-        <v>-3.9472961172150463</v>
+        <v>-265.67180859077553</v>
       </c>
       <c r="G8" s="0">
         <v>700</v>
       </c>
       <c r="H8" s="0">
-        <v>6998.523556227703</v>
+        <v>6433.134524807916</v>
       </c>
       <c r="I8" s="0">
-        <v>-3.9472961172150463</v>
+        <v>81.912283537515691</v>
       </c>
       <c r="J8" s="0">
-        <v>700</v>
+        <v>655.89999999999998</v>
       </c>
       <c r="K8" s="0">
-        <v>0.092370605468751421</v>
+        <v>2.9813293457031236</v>
       </c>
       <c r="L8" s="0" t="s">
         <v>17</v>
@@ -444,34 +444,34 @@
         <v>3</v>
       </c>
       <c r="B9" s="0">
-        <v>71.56781671856767</v>
+        <v>82</v>
       </c>
       <c r="C9" s="0">
-        <v>72.61140725458516</v>
+        <v>117</v>
       </c>
       <c r="D9" s="0">
         <v>2</v>
       </c>
       <c r="E9" s="0">
-        <v>7021.4819743656244</v>
+        <v>6400.5680191832607</v>
       </c>
       <c r="F9" s="0">
-        <v>64.939041425838695</v>
+        <v>-149.81044454801213</v>
       </c>
       <c r="G9" s="0">
         <v>700</v>
       </c>
       <c r="H9" s="0">
-        <v>7021.4819743656244</v>
+        <v>6424.9928984017524</v>
       </c>
       <c r="I9" s="0">
-        <v>64.939041425838695</v>
+        <v>23.98160151613348</v>
       </c>
       <c r="J9" s="0">
-        <v>700</v>
+        <v>688.97500000000002</v>
       </c>
       <c r="K9" s="0">
-        <v>0</v>
+        <v>2.2277954101562401</v>
       </c>
       <c r="L9" s="0" t="s">
         <v>17</v>
@@ -482,28 +482,28 @@
         <v>3</v>
       </c>
       <c r="B10" s="0">
-        <v>71.56781671856767</v>
+        <v>82</v>
       </c>
       <c r="C10" s="0">
-        <v>72.61140725458516</v>
+        <v>117</v>
       </c>
       <c r="D10" s="0">
         <v>3</v>
       </c>
       <c r="E10" s="0">
-        <v>7044.4403925035467</v>
+        <v>6416.8512719955879</v>
       </c>
       <c r="F10" s="0">
-        <v>133.82537896889289</v>
+        <v>-33.949080505248276</v>
       </c>
       <c r="G10" s="0">
         <v>700</v>
       </c>
       <c r="H10" s="0">
-        <v>7044.4403925035467</v>
+        <v>6416.8512719955879</v>
       </c>
       <c r="I10" s="0">
-        <v>133.82537896889289</v>
+        <v>-33.949080505248276</v>
       </c>
       <c r="J10" s="0">
         <v>700</v>
@@ -529,7 +529,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="0">
-        <v>13800</v>
+        <v>12680</v>
       </c>
       <c r="F11" s="0">
         <v>2000</v>
@@ -538,13 +538,13 @@
         <v>1800</v>
       </c>
       <c r="H11" s="0">
-        <v>14220</v>
+        <v>12995</v>
       </c>
       <c r="I11" s="0">
         <v>2000</v>
       </c>
       <c r="J11" s="0">
-        <v>1623.5999999999999</v>
+        <v>1700.7750000000001</v>
       </c>
       <c r="K11" s="0">
         <v>0</v>
@@ -567,7 +567,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="0">
-        <v>13870</v>
+        <v>12750</v>
       </c>
       <c r="F12" s="0">
         <v>2000</v>
@@ -576,7 +576,7 @@
         <v>1800</v>
       </c>
       <c r="H12" s="0">
-        <v>13870</v>
+        <v>12750</v>
       </c>
       <c r="I12" s="0">
         <v>2000</v>
@@ -605,7 +605,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="0">
-        <v>13940</v>
+        <v>12820</v>
       </c>
       <c r="F13" s="0">
         <v>2000</v>
@@ -614,7 +614,7 @@
         <v>1800</v>
       </c>
       <c r="H13" s="0">
-        <v>13940</v>
+        <v>12820</v>
       </c>
       <c r="I13" s="0">
         <v>2000</v>
@@ -634,34 +634,34 @@
         <v>5</v>
       </c>
       <c r="B14" s="0">
-        <v>113.35178634132112</v>
+        <v>117.99999999999999</v>
       </c>
       <c r="C14" s="0">
-        <v>99.789756281771815</v>
+        <v>122</v>
       </c>
       <c r="D14" s="0">
         <v>1</v>
       </c>
       <c r="E14" s="0">
-        <v>12313.361576158213</v>
+        <v>12232.507889157627</v>
       </c>
       <c r="F14" s="0">
-        <v>-409.60179695491866</v>
+        <v>-556.55727519422612</v>
       </c>
       <c r="G14" s="0">
         <v>1300</v>
       </c>
       <c r="H14" s="0">
-        <v>12313.361576158213</v>
+        <v>12146.594593167809</v>
       </c>
       <c r="I14" s="0">
-        <v>-409.60179695491866</v>
+        <v>-394.97786570104245</v>
       </c>
       <c r="J14" s="0">
-        <v>1300</v>
+        <v>1288.9749999999999</v>
       </c>
       <c r="K14" s="0">
-        <v>1.7424865722656264</v>
+        <v>3.6283813476562479</v>
       </c>
       <c r="L14" s="0" t="s">
         <v>19</v>
@@ -672,28 +672,28 @@
         <v>5</v>
       </c>
       <c r="B15" s="0">
-        <v>113.35178634132112</v>
+        <v>117.99999999999999</v>
       </c>
       <c r="C15" s="0">
-        <v>99.789756281771815</v>
+        <v>122</v>
       </c>
       <c r="D15" s="0">
         <v>2</v>
       </c>
       <c r="E15" s="0">
-        <v>12273.807364466364</v>
+        <v>12175.232358497748</v>
       </c>
       <c r="F15" s="0">
-        <v>-317.98596974033831</v>
+        <v>-448.83766886543685</v>
       </c>
       <c r="G15" s="0">
         <v>1300</v>
       </c>
       <c r="H15" s="0">
-        <v>12273.807364466364</v>
+        <v>12175.232358497748</v>
       </c>
       <c r="I15" s="0">
-        <v>-317.98596974033831</v>
+        <v>-448.83766886543685</v>
       </c>
       <c r="J15" s="0">
         <v>1300</v>
@@ -710,28 +710,28 @@
         <v>5</v>
       </c>
       <c r="B16" s="0">
-        <v>113.35178634132112</v>
+        <v>117.99999999999999</v>
       </c>
       <c r="C16" s="0">
-        <v>99.789756281771815</v>
+        <v>122</v>
       </c>
       <c r="D16" s="0">
         <v>3</v>
       </c>
       <c r="E16" s="0">
-        <v>12234.253152774516</v>
+        <v>12117.956827837868</v>
       </c>
       <c r="F16" s="0">
-        <v>-226.37014252575818</v>
+        <v>-341.11806253664781</v>
       </c>
       <c r="G16" s="0">
         <v>1300</v>
       </c>
       <c r="H16" s="0">
-        <v>12234.253152774516</v>
+        <v>12117.956827837868</v>
       </c>
       <c r="I16" s="0">
-        <v>-226.37014252575818</v>
+        <v>-341.11806253664781</v>
       </c>
       <c r="J16" s="0">
         <v>1300</v>
